--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/09_programs_initiatives.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/09_programs_initiatives.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rc1984e01364b4f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R3c30cec414d0477e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rcdc2a7aac9e14366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R8648df0327ad4694"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R47889352b4ff44e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R4b7dfbad51c24177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Re0330acac9a84106"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R91420c2f5bec4b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R801a07cbae9343cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rf7aac4cedd5540a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R3366f9ef9e334344"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rff9bd72e94614a13"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R544707022aed4700"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00c8531093b64230"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -809,7 +809,7 @@
         <x:v>Executive Office cycle time; Executive Office quality and exception rate; Executive Office adoption / utilization</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Enterprise profile and corporate priorities modernization and readiness program (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for programs initiatives.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -859,7 +859,7 @@
         <x:v>Provider Operations cycle time; Provider Operations quality and exception rate; Provider Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm Provider / clinical operations modernization and readiness program (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this programs initiatives record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>High</x:v>
@@ -909,7 +909,7 @@
         <x:v>Claims Operations cycle time; Claims Operations quality and exception rate; Claims Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Attach client evidence for Payer / claims operations modernization and readiness program (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>High</x:v>
@@ -959,7 +959,7 @@
         <x:v>Eligibility and Benefits cycle time; Eligibility and Benefits quality and exception rate; Eligibility and Benefits adoption / utilization</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Reconcile Eligibility / benefits modernization and readiness program (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>High</x:v>
@@ -1009,7 +1009,7 @@
         <x:v>Prior Authorization and UM cycle time; Prior Authorization and UM quality and exception rate; Prior Authorization and UM adoption / utilization</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior authorization / utilization management modernization and readiness program (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>High</x:v>
@@ -1059,7 +1059,7 @@
         <x:v>Contact Center and Member Service cycle time; Contact Center and Member Service quality and exception rate; Contact Center and Member Service adoption / utilization</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Member experience / contact center modernization and readiness program (record 6) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>Medium</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>Revenue Cycle Operations cycle time; Revenue Cycle Operations quality and exception rate; Revenue Cycle Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm Revenue cycle modernization and readiness program (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this programs initiatives record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>High</x:v>
@@ -1159,7 +1159,7 @@
         <x:v>Finance Analytics cycle time; Finance Analytics quality and exception rate; Finance Analytics adoption / utilization</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Finance analytics modernization and readiness program (record 8) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>High</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>Workforce Analytics cycle time; Workforce Analytics quality and exception rate; Workforce Analytics adoption / utilization</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Reconcile HR / workforce analytics modernization and readiness program (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>High</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>Clinical Quality Analytics cycle time; Clinical Quality Analytics quality and exception rate; Clinical Quality Analytics adoption / utilization</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical quality analytics modernization and readiness program (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>High</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>Claims and Payment Analytics cycle time; Claims and Payment Analytics quality and exception rate; Claims and Payment Analytics adoption / utilization</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Claims analytics modernization and readiness program (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for programs initiatives.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>Medium</x:v>
@@ -1359,7 +1359,7 @@
         <x:v>Provider Performance Analytics cycle time; Provider Performance Analytics quality and exception rate; Provider Performance Analytics adoption / utilization</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm Provider performance analytics modernization and readiness program (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this programs initiatives record is used downstream.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>High</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>Enterprise Data Platform cycle time; Enterprise Data Platform quality and exception rate; Enterprise Data Platform adoption / utilization</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Attach client evidence for Enterprise data platform / lakehouse modernization and readiness program (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>High</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>Data Governance and Data Quality cycle time; Data Governance and Data Quality quality and exception rate; Data Governance and Data Quality adoption / utilization</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Reconcile Data governance, quality, catalog, MDM modernization and readiness program (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>High</x:v>
@@ -1509,7 +1509,7 @@
         <x:v>Agent Assist and Next Best Action cycle time; Agent Assist and Next Best Action quality and exception rate; Agent Assist and Next Best Action adoption / utilization</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Agent Assist for member service modernization and readiness program (record 15) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>High</x:v>
@@ -1559,7 +1559,7 @@
         <x:v>Unified Clinical and Claims Lakehouse cycle time; Unified Clinical and Claims Lakehouse quality and exception rate; Unified Clinical and Claims Lakehouse adoption / utilization</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Unified clinical + claims lakehouse modernization and readiness program (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for programs initiatives.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>Medium</x:v>
@@ -1609,7 +1609,7 @@
         <x:v>IT Budget and Tower Baseline cycle time; IT Budget and Tower Baseline quality and exception rate; IT Budget and Tower Baseline adoption / utilization</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm IT budget and Tower spend baseline modernization and readiness program (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this programs initiatives record is used downstream.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>High</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>Vendor and Contract Optimization cycle time; Vendor and Contract Optimization quality and exception rate; Vendor and Contract Optimization adoption / utilization</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Attach client evidence for Vendor / contract / sourcing context modernization and readiness program (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>High</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>Infrastructure and CMDB cycle time; Infrastructure and CMDB quality and exception rate; Infrastructure and CMDB adoption / utilization</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Reconcile CMDB / infrastructure / cloud inventory context modernization and readiness program (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>High</x:v>
@@ -1759,7 +1759,7 @@
         <x:v>Incident Problem Change Operations cycle time; Incident Problem Change Operations quality and exception rate; Incident Problem Change Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident / problem / change operational health context modernization and readiness program (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>High</x:v>
@@ -1780,7 +1780,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R071afe6b4c1e4cb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87c78f16b07848d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1855,7 +1855,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba7771f1151541ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02eb17837bfc40fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2049,7 +2049,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5e66d0cfd514ab0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29f4200e33eb48d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2111,7 +2111,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a068585c4dd484e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc86db29be9b34ef1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2221,7 +2221,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2e45f84d2204447"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4270cce0ec534401"/>
   </x:tableParts>
 </x:worksheet>
 </file>